--- a/doc/ini/単体テスト仕様書.xlsx
+++ b/doc/ini/単体テスト仕様書.xlsx
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -95,6 +95,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -482,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>src/components/CouponList.jsx（リワードクーポンマスタ一覧画面）</t>
+          <t>設計書[管理]ー71.CouponList一覧.xlsx</t>
         </is>
       </c>
     </row>
@@ -496,7 +502,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Deivaraj</t>
+          <t>カルティク</t>
         </is>
       </c>
     </row>
@@ -543,748 +549,591 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>初期表示</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">検索条件部が表示される。</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+          <t>検索条件部が表示される。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　クーポンID：初期値なし、テキストフィールド</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　クーポン名称：初期値なし、テキストフィールド</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="5" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　期間（開始日）：初期値なし、日付入力</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　_review_needed: could not determine field name (unlabeled date input #1)：初期値なし、テキストフィールド、カレンダー表示</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　期間（終了日）：初期値なし、日付入力</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　_review_needed: could not determine field name (unlabeled date input #2)：初期値なし、テキストフィールド、カレンダー表示</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　種別：初期値あり「すべて」、ラジオボタン「すべて／QR／来店」</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="5" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　承認：初期値あり「すべて」、ラジオボタン「すべて／未承認／承認」</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>一覧表示</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>検索結果一覧に以下の列が表示される。</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　クーポンID／ソート可</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　クーポンコード</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　クーポン名称</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　期間</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　種別</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　承認</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+      <c r="F22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　操作</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>「検索」ボタン</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">検索処理を実行し、検索結果が一覧表示される。</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　抽出条件：検索条件によるAND検索。</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>検索処理を実行し、CouponList一覧表示される。</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="7" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　抽出条件：論理削除データを含まない、かつ、検索条件（AND検索）。</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr"/>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　クーポンID：完全一致</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　クーポン名称：部分一致</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　期間（開始日）：終了日が開始日以降のデータが対象（範囲一致）。</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　期間（終了日）：開始日が終了日以前のデータが対象（範囲一致）。</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　種別：完全一致（「すべて」選択時は絞り込みなし）。</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　承認：完全一致（「すべて」選択時は絞り込みなし）。</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　初期表示時は、クーポンIDの降順でソートされる。</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr"/>
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr"/>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　クーポン名称：完全一致</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr"/>
+      <c r="E27" s="7" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　_review_needed: could not determine field name (unlabeled date input #1)：完全一致</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr"/>
+      <c r="E28" s="7" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　_review_needed: could not determine field name (unlabeled date input #2)：完全一致</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr"/>
+      <c r="E29" s="7" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr"/>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　種別：完全一致</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr"/>
+      <c r="E30" s="7" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　承認：完全一致</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr"/>
+      <c r="E31" s="7" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr"/>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ソート：クーポンIDの降順。</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr"/>
+      <c r="F32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>検索処理後、検索エリアに入力した検索条件が正しく表示される。</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">件数が20件以下の場合、ページネートされない。</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>件数が20件以下の場合、ページネートされない。</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　件数が21件以上の場合、ページネートされる。</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　最初のページの場合、「最初」「前へ」ボタンが表示されない。</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　最後のページの場合、「次へ」「最後」ボタンが表示されない。</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　上記以外の場合、「最初」「前へ」「次へ」「最後」ボタンが表示される。</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　「全○件」が正しく表示される。</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　現在ページの「○件〜○件」が正しく表示される。</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="7" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　最初のページの場合、「最初」「前へ」リンクが表示されない。</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr"/>
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　最後のページの場合、「最後」「次へ」リンクが表示されない。</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr"/>
+      <c r="E37" s="7" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr"/>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　上記以外の場合、「最初」「前へ」「最後」「次へ」リンクが表示される。</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr"/>
+      <c r="E38" s="7" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ページネートはそれぞれボタン表示されるが、現在のページはテキストのみで表示される。</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr"/>
+      <c r="E39" s="7" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr"/>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>「全○件」が正しく表示される。</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr"/>
+      <c r="E40" s="7" t="inlineStr"/>
+      <c r="F40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>現在ページの「○件～○件」が正しく表示される。</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr"/>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>ページ遷移時、ページ番号がURLパラメータとして引き継がれる。</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr"/>
+      <c r="E42" s="7" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>ソート</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「クーポンID」列見出しをクリックすると昇順・降順が切り替わる。</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>クーポン名称リンク</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">クリックするとクーポン詳細画面へ遷移する。</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>「クーポンID」をクリックで昇順・降順が切替えられる。</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr"/>
+      <c r="E43" s="7" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr"/>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>ソート処理後、検索エリアに入力した検索条件が正しく表示される。</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr"/>
+      <c r="E44" s="7" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>「新規登録」ボタン</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">クーポン登録画面へ遷移する。
-※ログインユーザーが「管理者」または「利用者」の場合のみ表示される。</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>CouponForm登録へ遷移する。</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr"/>
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>「編集」ボタン</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">クーポン編集画面へ遷移する。対象のIDが引き継がれる。
-※ログインユーザーが「管理者」または「利用者」の場合のみ表示される。</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>CouponForm編集へ遷移する。
+対象のIDがURLパラメータとして引き継がれる。</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr"/>
+      <c r="E46" s="7" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>「削除」ボタン</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">確認ダイアログが表示される。
-※ログインユーザーが「管理者」または「利用者」の場合のみ表示される。</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr"/>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　「OK」の場合、対象データが削除され、一覧が再検索される。</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B38" s="5" t="inlineStr"/>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　「キャンセル」の場合、何も実行されない。</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr"/>
-    </row>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>（動作を記載）</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr"/>
+      <c r="E47" s="7" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>テスト対象の設計書</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>src/components/CouponForm.jsx（mode="register"）（リワードクーポンマスタ登録画面）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>担当者</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Deivaraj</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>分類</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>確認内容（期待する結果）</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>OK/NG</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>確認日</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>初期表示</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">以下が表示される。</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　クーポンID：「自動採番」、入力不可</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　クーポン名称：初期値なし、テキストフィールド</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　期間（開始日）：初期値なし、日付入力</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　期間（終了日）：初期値なし、日付入力</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　詳細：初期値なし、テキストエリア</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　種別：初期値あり「来店」、ラジオボタン「来店／QR」</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　承認：初期値あり「未承認」、ラジオボタン「承認／未承認」</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>「確認」ボタン</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力値検証NGの場合、エラーメッセージが表示される。</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　クーポン名称が未入力の場合「クーポン名称は必須です。」が表示される。</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　期間（開始日）が未入力の場合「期間（開始日）は必須です。」が表示される。</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　期間（終了日）が未入力の場合「期間（終了日）は必須です。」が表示される。</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　入力値検証OKの場合、登録確認画面へ遷移し、入力値が引き継がれる。</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1311,7 +1160,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>src/components/CouponConfirm.jsx（mode="register"）（リワードクーポンマスタ登録確認画面）</t>
+          <t>設計書[管理]ー71.CouponForm登録.xlsx</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1174,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Deivaraj</t>
+          <t>カルティク</t>
         </is>
       </c>
     </row>
@@ -1372,183 +1221,166 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>初期表示</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力内容の確認部が表示される。</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+          <t>以下が表示される。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　クーポンID：「自動採番」</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　クーポンID：初期値なし、テキストフィールド</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　クーポン名称：入力値</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　クーポンコード：初期値なし、テキストフィールド</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="5" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　期間（開始日）：入力値</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　クーポン名称：初期値なし、テキストフィールド</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　期間（終了日）：入力値</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　期間（開始日）：初期値なし、テキストフィールド、カレンダー表示</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　種別：選択値「来店／QR」</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　期間（終了日）：初期値なし、テキストフィールド、カレンダー表示</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="5" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　承認：選択値「承認／未承認」</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　詳細：初期値なし、テキストエリア</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　詳細：確認画面には表示されない（画面上に項目なし）。</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　種別：初期値あり「来店」、ラジオボタン「来店／QR」</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>「修正する」ボタン</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">登録入力画面へ遷移し、入力値が復元される。</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　承認：初期値あり「承認」、ラジオボタン「承認／未承認」</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>「登録する」ボタン</t>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>「確認」ボタン</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">登録処理を実行し、一覧画面へ遷移する。</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　クーポンIDは登録時に自動採番される（既存の最大IDの次番）。</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-    </row>
+          <t>（動作を記載）</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1569,7 +1401,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>src/components/CouponDetail.jsx（リワードクーポンマスタ詳細画面）</t>
+          <t>設計書[管理]ー71.CouponConfirm登録確認.xlsx</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1415,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Deivaraj</t>
+          <t>カルティク</t>
         </is>
       </c>
     </row>
@@ -1630,158 +1462,386 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>初期表示</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">詳細部が表示される。</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+          <t>詳細部が表示される。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">　クーポンID：入力値</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　クーポン名称：入力値</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　期間（開始日）：入力値</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　期間（終了日）：入力値</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　種別：入力値</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　承認：入力値</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>「修正する」ボタン</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>（動作を記載）</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>テスト対象の設計書</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>設計書[管理]ー71.CouponDetail詳細.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>カルティク</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>確認内容（期待する結果）</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>OK/NG</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>確認日</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>初期表示</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>詳細部が表示される。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">　クーポンID：保存値</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">　クーポンコード：保存値</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">　クーポン名称：保存値</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　期間（開始日）：保存値</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　期間（終了日）：保存値</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　詳細：保存値</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　種別：保存値「来店／QR」</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　承認：保存値「承認／未承認」</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　種別：保存値</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　承認：保存値</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>「一覧へ戻る」ボタン</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">クーポン一覧画面へ遷移する。</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>CouponList一覧へ遷移する。</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>「編集」ボタン</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">クーポン編集画面へ遷移する。対象のIDが引き継がれる。
-※ログインユーザーが「管理者」または「利用者」の場合のみ表示される。</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-    </row>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>CouponForm編集へ遷移する。
+対象のIDがURLパラメータとして引き継がれる。</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1814,7 +1874,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>src/components/CouponForm.jsx（mode="edit"）（リワードクーポンマスタ編集画面）</t>
+          <t>設計書[管理]ー71.CouponForm編集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1888,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Deivaraj</t>
+          <t>カルティク</t>
         </is>
       </c>
     </row>
@@ -1875,167 +1935,154 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>初期表示</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">以下が表示される。</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+          <t>以下が表示される。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　クーポンID：「対象データのID」、入力不可</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　クーポンID：初期値なし、テキストフィールド</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　クーポン名称：保存値が初期表示される、テキストフィールド</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　クーポンコード：初期値なし、テキストフィールド</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="5" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　期間（開始日）：保存値が初期表示される、日付入力</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　クーポン名称：初期値なし、テキストフィールド</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　期間（終了日）：保存値が初期表示される、日付入力</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　期間（開始日）：初期値なし、テキストフィールド、カレンダー表示</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　詳細：保存値が初期表示される、テキストエリア</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　期間（終了日）：初期値なし、テキストフィールド、カレンダー表示</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="5" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　種別：保存値が初期表示される、ラジオボタン「来店／QR」</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　詳細：初期値なし、テキストエリア</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　承認：保存値が初期表示される、ラジオボタン「承認／未承認」</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　種別：初期値あり「来店」、ラジオボタン「来店／QR」</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="5" t="inlineStr"/>
+      <c r="B17" s="8" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　編集確認画面から「修正する」で戻った場合は、保存値ではなく直前の入力値が復元される。</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　承認：初期値あり「承認」、ラジオボタン「承認／未承認」</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>「確認」ボタン</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力値検証NGの場合、エラーメッセージが表示される（登録画面と同条件）。</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　入力値検証OKの場合、編集確認画面へ遷移し、入力値が引き継がれる。</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-    </row>
+          <t>（動作を記載）</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2047,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2068,7 +2115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>src/components/CouponConfirm.jsx（mode="edit"）（リワードクーポンマスタ編集確認画面）</t>
+          <t>設計書[管理]ー71.CouponConfirm編集確認.xlsx</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2129,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Deivaraj</t>
+          <t>カルティク</t>
         </is>
       </c>
     </row>
@@ -2129,157 +2176,126 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>初期表示</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更内容の確認部が表示される。</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+          <t>詳細部が表示される。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　クーポンID：対象データのID</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　クーポンID：入力値</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　クーポン名称：入力値</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="5" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　期間（開始日）：入力値</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　期間（終了日）：入力値</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　種別：選択値「来店／QR」</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　種別：入力値</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="5" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　承認：選択値「承認／未承認」</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
+          <t xml:space="preserve">　承認：入力値</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>「修正する」ボタン</t>
+        </is>
+      </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　詳細：確認画面には表示されない（画面上に項目なし）。</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>「修正する」ボタン</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">編集入力画面へ遷移し、入力値が復元される。</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>「更新する」ボタン</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">更新処理を実行し、一覧画面へ遷移する。</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-    </row>
+          <t>（動作を記載）</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
